--- a/Sensitivity analysis/figure7.xlsx
+++ b/Sensitivity analysis/figure7.xlsx
@@ -425,37 +425,37 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.077025</v>
+        <v>0.09279336734693877</v>
       </c>
       <c r="C2">
-        <v>0.076975</v>
+        <v>0.09275793650793651</v>
       </c>
       <c r="D2">
-        <v>0.07667499999999999</v>
+        <v>0.09250992063492064</v>
       </c>
       <c r="E2">
-        <v>0.07642500000000001</v>
+        <v>0.09222647392290249</v>
       </c>
       <c r="F2">
-        <v>0.0766</v>
+        <v>0.09268707482993198</v>
       </c>
       <c r="G2">
-        <v>0.076725</v>
+        <v>0.09311224489795919</v>
       </c>
       <c r="H2">
-        <v>0.077075</v>
+        <v>0.09367913832199547</v>
       </c>
       <c r="I2">
-        <v>0.07729999999999999</v>
+        <v>0.09392715419501134</v>
       </c>
       <c r="J2">
-        <v>0.07745</v>
+        <v>0.0946357709750567</v>
       </c>
       <c r="K2">
-        <v>0.078125</v>
+        <v>0.0954861111111111</v>
       </c>
       <c r="L2">
-        <v>0.078975</v>
+        <v>0.09654903628117914</v>
       </c>
     </row>
     <row r="3">
@@ -465,37 +465,37 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.2675</v>
+        <v>0.3006306689342403</v>
       </c>
       <c r="C3">
-        <v>0.262975</v>
+        <v>0.2952097505668934</v>
       </c>
       <c r="D3">
-        <v>0.251975</v>
+        <v>0.2848639455782313</v>
       </c>
       <c r="E3">
-        <v>0.235675</v>
+        <v>0.2689200680272109</v>
       </c>
       <c r="F3">
-        <v>0.2178</v>
+        <v>0.2523030045351474</v>
       </c>
       <c r="G3">
-        <v>0.199675</v>
+        <v>0.2329577664399093</v>
       </c>
       <c r="H3">
-        <v>0.1808</v>
+        <v>0.2120535714285714</v>
       </c>
       <c r="I3">
-        <v>0.1641</v>
+        <v>0.1915745464852608</v>
       </c>
       <c r="J3">
-        <v>0.14775</v>
+        <v>0.1725481859410431</v>
       </c>
       <c r="K3">
-        <v>0.1337</v>
+        <v>0.1564271541950113</v>
       </c>
       <c r="L3">
-        <v>0.1222</v>
+        <v>0.1437074829931973</v>
       </c>
     </row>
   </sheetData>
@@ -577,37 +577,37 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.077025</v>
+        <v>0.09279336734693877</v>
       </c>
       <c r="C2">
-        <v>0.07679999999999999</v>
+        <v>0.09279336734693877</v>
       </c>
       <c r="D2">
-        <v>0.07635</v>
+        <v>0.09325396825396826</v>
       </c>
       <c r="E2">
-        <v>0.07552499999999999</v>
+        <v>0.09350198412698413</v>
       </c>
       <c r="F2">
-        <v>0.0743</v>
+        <v>0.09204931972789115</v>
       </c>
       <c r="G2">
-        <v>0.07495</v>
+        <v>0.09346655328798185</v>
       </c>
       <c r="H2">
-        <v>0.075825</v>
+        <v>0.0939625850340136</v>
       </c>
       <c r="I2">
-        <v>0.076975</v>
+        <v>0.09481292517006802</v>
       </c>
       <c r="J2">
-        <v>0.0759</v>
+        <v>0.09328939909297052</v>
       </c>
       <c r="K2">
-        <v>0.04915</v>
+        <v>0.0586734693877551</v>
       </c>
       <c r="L2">
-        <v>0.0786</v>
+        <v>0.0954861111111111</v>
       </c>
     </row>
     <row r="3">
@@ -617,37 +617,37 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.2675</v>
+        <v>0.3006306689342403</v>
       </c>
       <c r="C3">
-        <v>0.268575</v>
+        <v>0.3013038548752834</v>
       </c>
       <c r="D3">
-        <v>0.269825</v>
+        <v>0.3022250566893424</v>
       </c>
       <c r="E3">
-        <v>0.27075</v>
+        <v>0.3035359977324263</v>
       </c>
       <c r="F3">
-        <v>0.271875</v>
+        <v>0.3050240929705215</v>
       </c>
       <c r="G3">
-        <v>0.27345</v>
+        <v>0.3062996031746032</v>
       </c>
       <c r="H3">
-        <v>0.274475</v>
+        <v>0.3072562358276644</v>
       </c>
       <c r="I3">
-        <v>0.27535</v>
+        <v>0.308531746031746</v>
       </c>
       <c r="J3">
-        <v>0.2773</v>
+        <v>0.3104804421768708</v>
       </c>
       <c r="K3">
-        <v>0.27995</v>
+        <v>0.3138463718820862</v>
       </c>
       <c r="L3">
-        <v>0.28215</v>
+        <v>0.3160076530612245</v>
       </c>
     </row>
   </sheetData>
@@ -729,37 +729,37 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.077025</v>
+        <v>0.09279336734693877</v>
       </c>
       <c r="C2">
-        <v>0.07679999999999999</v>
+        <v>0.09282879818594104</v>
       </c>
       <c r="D2">
-        <v>0.07645</v>
+        <v>0.09346655328798185</v>
       </c>
       <c r="E2">
-        <v>0.076</v>
+        <v>0.09431689342403628</v>
       </c>
       <c r="F2">
-        <v>0.07580000000000001</v>
+        <v>0.09406887755102041</v>
       </c>
       <c r="G2">
-        <v>0.07765</v>
+        <v>0.09686791383219955</v>
       </c>
       <c r="H2">
-        <v>0.079625</v>
+        <v>0.0988874716553288</v>
       </c>
       <c r="I2">
-        <v>0.082</v>
+        <v>0.101296768707483</v>
       </c>
       <c r="J2">
-        <v>0.0818</v>
+        <v>0.1014384920634921</v>
       </c>
       <c r="K2">
-        <v>0.05215</v>
+        <v>0.06242913832199547</v>
       </c>
       <c r="L2">
-        <v>0.08525000000000001</v>
+        <v>0.1047689909297052</v>
       </c>
     </row>
     <row r="3">
@@ -769,37 +769,37 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.2675</v>
+        <v>0.3006306689342403</v>
       </c>
       <c r="C3">
-        <v>0.264075</v>
+        <v>0.2963081065759637</v>
       </c>
       <c r="D3">
-        <v>0.2545</v>
+        <v>0.2868835034013605</v>
       </c>
       <c r="E3">
-        <v>0.23925</v>
+        <v>0.2726757369614513</v>
       </c>
       <c r="F3">
-        <v>0.222575</v>
+        <v>0.2577593537414966</v>
       </c>
       <c r="G3">
-        <v>0.205725</v>
+        <v>0.2394770408163265</v>
       </c>
       <c r="H3">
-        <v>0.1883</v>
+        <v>0.2197066326530612</v>
       </c>
       <c r="I3">
-        <v>0.1721</v>
+        <v>0.1997945011337869</v>
       </c>
       <c r="J3">
-        <v>0.156775</v>
+        <v>0.1820082199546485</v>
       </c>
       <c r="K3">
-        <v>0.144325</v>
+        <v>0.1674815759637188</v>
       </c>
       <c r="L3">
-        <v>0.1345</v>
+        <v>0.1569940476190476</v>
       </c>
     </row>
   </sheetData>
